--- a/copilot-excel-skills-demo.xlsx
+++ b/copilot-excel-skills-demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC0E499D-35C0-480A-8F1F-E49B420961C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F58019-356A-424B-BBE8-940C9F47F19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="115">
   <si>
     <t>STRINGFEST ANALYTICS</t>
   </si>
@@ -331,18 +331,93 @@
   <si>
     <t>Materiality is keyed to the variance vs budget, matching the skill's rule.</t>
   </si>
+  <si>
+    <t>Unit Economics — Copilot Analysis</t>
+  </si>
+  <si>
+    <t>Live formulas based on the yellow input cells above; change the inputs and this section recalculates.</t>
+  </si>
+  <si>
+    <t>Interpretation</t>
+  </si>
+  <si>
+    <t>S&amp;M spend divided by new customers acquired.</t>
+  </si>
+  <si>
+    <t>Monthly gross profit per customer</t>
+  </si>
+  <si>
+    <t>Monthly ARPU multiplied by gross margin.</t>
+  </si>
+  <si>
+    <t>Average customer lifetime</t>
+  </si>
+  <si>
+    <t>Inverse of monthly churn rate.</t>
+  </si>
+  <si>
+    <t>Monthly gross profit per customer multiplied by expected lifetime.</t>
+  </si>
+  <si>
+    <t>Above 3.0x is generally healthy; above 5.0x is strong.</t>
+  </si>
+  <si>
+    <t>CAC payback period</t>
+  </si>
+  <si>
+    <t>Months required for gross profit to recover CAC.</t>
+  </si>
+  <si>
+    <t>Health read</t>
+  </si>
+  <si>
+    <t>Variance Commentary — Actual vs Budget vs Prior</t>
+  </si>
+  <si>
+    <t>Materiality: flag budget variances greater than $10,000 or 5% of budget; table sorted by largest absolute budget variance.</t>
+  </si>
+  <si>
+    <t>Abs $ vs Bud</t>
+  </si>
+  <si>
+    <t>Commentary</t>
+  </si>
+  <si>
+    <t>Total operating expenses were $55,000 over budget (+7.9%) and $50,000 above prior month (+7.1%), making expense growth the largest pressure point on the period.</t>
+  </si>
+  <si>
+    <t>Revenue was $40,000 above budget (+3.3%) and $60,000 above prior month (+5.1%), showing stronger top-line activity than planned.</t>
+  </si>
+  <si>
+    <t>Sales &amp; marketing was $40,000 over budget (+16.7%) and $30,000 above prior month (+12.0%), suggesting incremental acquisition or campaign spend drove most of the expense overrun.</t>
+  </si>
+  <si>
+    <t>Gross profit was $34,000 above budget (+3.8%) and $49,000 above prior month (+5.5%), consistent with revenue upside more than offsetting cost of revenue growth.</t>
+  </si>
+  <si>
+    <t>Operating income was $21,000 below budget (-10.2%) and $1,000 below prior month (-0.5%), as the expense overrun absorbed nearly all of the revenue and gross profit upside.</t>
+  </si>
+  <si>
+    <t>General &amp; administrative was $15,000 over budget (+10.0%) and $13,000 above prior month (+8.6%), indicating overhead ran above plan.</t>
+  </si>
+  <si>
+    <t>Overall, the month delivered healthy revenue and gross profit growth, but operating leverage did not flow through because operating expenses rose faster than plan. The main management focus is controlling sales &amp; marketing and G&amp;A spend so revenue upside converts into operating income.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
     <numFmt numFmtId="165" formatCode="0.0%;\(0.0%\)"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0\x"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -468,8 +543,62 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,8 +623,56 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F9F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -512,11 +689,102 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E1F2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E1F2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9EAF7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9EAF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9EAF7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9EAF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF5B9BD5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9EAD3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9EAD3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9EAD3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9EAD3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -595,11 +863,91 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="22" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -678,6 +1026,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1029,13 +1381,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:D12"/>
+  <dimension ref="B2:D27"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" customWidth="1"/>
+    <col min="3" max="3" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="20.65" x14ac:dyDescent="0.6">
@@ -1119,7 +1471,130 @@
         <v>46</v>
       </c>
     </row>
+    <row r="14" spans="2:4" ht="21" x14ac:dyDescent="0.65">
+      <c r="B14" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B15" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B17" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B18" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="42">
+        <f>C7/C6</f>
+        <v>300</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B19" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="43">
+        <f>C8*C9</f>
+        <v>60</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B20" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="44">
+        <f>1/C10</f>
+        <v>25</v>
+      </c>
+      <c r="D20" s="46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B21" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="48">
+        <f>C8*C9/C10</f>
+        <v>1500</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B22" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="49">
+        <f>(C8*C9/C10)/(C7/C6)</f>
+        <v>5</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B23" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="50">
+        <f>(C7/C6)/(C8*C9)</f>
+        <v>5</v>
+      </c>
+      <c r="D23" s="47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B25" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B26" s="37" t="str">
+        <f>IF(C22&gt;=3,"Healthy: LTV:CAC is "&amp;TEXT(C22,"0.0x")&amp;", above the 3.0x SaaS benchmark, and CAC payback is "&amp;TEXT(C23,"0.0")&amp;" months. The combination of $"&amp;TEXT(C18,"#,##0")&amp;" CAC, $"&amp;TEXT(C21,"#,##0")&amp;" LTV, and "&amp;TEXT(C10,"0.0%")&amp;" monthly churn points to attractive unit economics, assuming churn and acquisition efficiency hold.","Needs attention: LTV:CAC is "&amp;TEXT(C22,"0.0x")&amp;", below the 3.0x SaaS benchmark. Improve retention, ARPU, gross margin, or acquisition efficiency before scaling spend.")</f>
+        <v>Healthy: LTV:CAC is 5.0x, above the 3.0x SaaS benchmark, and CAC payback is 5.0 months. The combination of $300 CAC, $1,500 LTV, and 4.0% monthly churn points to attractive unit economics, assuming churn and acquisition efficiency hold.</v>
+      </c>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D27"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -1237,25 +1712,49 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:E17"/>
+  <dimension ref="B2:O23"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="5" width="16" customWidth="1"/>
+    <col min="2" max="2" width="58.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.19921875" customWidth="1"/>
+    <col min="8" max="14" width="14.19921875" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="20.65" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:15" ht="21" x14ac:dyDescent="0.65">
       <c r="B2" s="9" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G2" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+    </row>
+    <row r="3" spans="2:15" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G3" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B5" s="11" t="s">
         <v>65</v>
       </c>
@@ -1268,8 +1767,35 @@
       <c r="E5" s="12" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G5" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="L5" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="N5" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="O5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B6" s="13" t="s">
         <v>69</v>
       </c>
@@ -1282,8 +1808,44 @@
       <c r="E6" s="23">
         <v>1180000</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G6" s="57" t="str">
+        <f>TRIM($B$15)</f>
+        <v>Total operating expenses</v>
+      </c>
+      <c r="H6" s="53">
+        <f>$C$15</f>
+        <v>750000</v>
+      </c>
+      <c r="I6" s="53">
+        <f>$D$15</f>
+        <v>695000</v>
+      </c>
+      <c r="J6" s="53">
+        <f>H6-I6</f>
+        <v>55000</v>
+      </c>
+      <c r="K6" s="54">
+        <f>IFERROR(J6/I6,0)</f>
+        <v>7.9136690647482008E-2</v>
+      </c>
+      <c r="L6" s="53">
+        <f>$E$15</f>
+        <v>700000</v>
+      </c>
+      <c r="M6" s="53">
+        <f>H6-L6</f>
+        <v>50000</v>
+      </c>
+      <c r="N6" s="54">
+        <f>IFERROR(M6/L6,0)</f>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="O6">
+        <f>ABS(J6)</f>
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B7" s="13" t="s">
         <v>70</v>
       </c>
@@ -1296,8 +1858,44 @@
       <c r="E7" s="23">
         <v>295000</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G7" s="57" t="str">
+        <f>TRIM($B$6)</f>
+        <v>Revenue</v>
+      </c>
+      <c r="H7" s="53">
+        <f>$C$6</f>
+        <v>1240000</v>
+      </c>
+      <c r="I7" s="53">
+        <f>$D$6</f>
+        <v>1200000</v>
+      </c>
+      <c r="J7" s="53">
+        <f>H7-I7</f>
+        <v>40000</v>
+      </c>
+      <c r="K7" s="54">
+        <f>IFERROR(J7/I7,0)</f>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="L7" s="53">
+        <f>$E$6</f>
+        <v>1180000</v>
+      </c>
+      <c r="M7" s="53">
+        <f>H7-L7</f>
+        <v>60000</v>
+      </c>
+      <c r="N7" s="54">
+        <f>IFERROR(M7/L7,0)</f>
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="O7">
+        <f>ABS(J7)</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B8" s="24" t="s">
         <v>71</v>
       </c>
@@ -1313,13 +1911,123 @@
         <f>E6-E7</f>
         <v>885000</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G8" s="57" t="str">
+        <f>TRIM($B$11)</f>
+        <v>Sales &amp; marketing</v>
+      </c>
+      <c r="H8" s="53">
+        <f>$C$11</f>
+        <v>280000</v>
+      </c>
+      <c r="I8" s="53">
+        <f>$D$11</f>
+        <v>240000</v>
+      </c>
+      <c r="J8" s="53">
+        <f>H8-I8</f>
+        <v>40000</v>
+      </c>
+      <c r="K8" s="54">
+        <f>IFERROR(J8/I8,0)</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="L8" s="53">
+        <f>$E$11</f>
+        <v>250000</v>
+      </c>
+      <c r="M8" s="53">
+        <f>H8-L8</f>
+        <v>30000</v>
+      </c>
+      <c r="N8" s="54">
+        <f>IFERROR(M8/L8,0)</f>
+        <v>0.12</v>
+      </c>
+      <c r="O8">
+        <f>ABS(J8)</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G9" s="57" t="str">
+        <f>TRIM($B$8)</f>
+        <v>Gross profit</v>
+      </c>
+      <c r="H9" s="53">
+        <f>$C$8</f>
+        <v>934000</v>
+      </c>
+      <c r="I9" s="53">
+        <f>$D$8</f>
+        <v>900000</v>
+      </c>
+      <c r="J9" s="53">
+        <f>H9-I9</f>
+        <v>34000</v>
+      </c>
+      <c r="K9" s="54">
+        <f>IFERROR(J9/I9,0)</f>
+        <v>3.7777777777777778E-2</v>
+      </c>
+      <c r="L9" s="53">
+        <f>$E$8</f>
+        <v>885000</v>
+      </c>
+      <c r="M9" s="53">
+        <f>H9-L9</f>
+        <v>49000</v>
+      </c>
+      <c r="N9" s="54">
+        <f>IFERROR(M9/L9,0)</f>
+        <v>5.5367231638418078E-2</v>
+      </c>
+      <c r="O9">
+        <f>ABS(J9)</f>
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B10" s="26" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G10" s="57" t="str">
+        <f>TRIM($B$17)</f>
+        <v>Operating income</v>
+      </c>
+      <c r="H10" s="53">
+        <f>$C$17</f>
+        <v>184000</v>
+      </c>
+      <c r="I10" s="53">
+        <f>$D$17</f>
+        <v>205000</v>
+      </c>
+      <c r="J10" s="53">
+        <f>H10-I10</f>
+        <v>-21000</v>
+      </c>
+      <c r="K10" s="54">
+        <f>IFERROR(J10/I10,0)</f>
+        <v>-0.1024390243902439</v>
+      </c>
+      <c r="L10" s="53">
+        <f>$E$17</f>
+        <v>185000</v>
+      </c>
+      <c r="M10" s="53">
+        <f>H10-L10</f>
+        <v>-1000</v>
+      </c>
+      <c r="N10" s="54">
+        <f>IFERROR(M10/L10,0)</f>
+        <v>-5.4054054054054057E-3</v>
+      </c>
+      <c r="O10">
+        <f>ABS(J10)</f>
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B11" s="13" t="s">
         <v>73</v>
       </c>
@@ -1332,8 +2040,44 @@
       <c r="E11" s="23">
         <v>250000</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G11" s="57" t="str">
+        <f>TRIM($B$13)</f>
+        <v>General &amp; administrative</v>
+      </c>
+      <c r="H11" s="53">
+        <f>$C$13</f>
+        <v>165000</v>
+      </c>
+      <c r="I11" s="53">
+        <f>$D$13</f>
+        <v>150000</v>
+      </c>
+      <c r="J11" s="53">
+        <f>H11-I11</f>
+        <v>15000</v>
+      </c>
+      <c r="K11" s="54">
+        <f>IFERROR(J11/I11,0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="L11" s="53">
+        <f>$E$13</f>
+        <v>152000</v>
+      </c>
+      <c r="M11" s="53">
+        <f>H11-L11</f>
+        <v>13000</v>
+      </c>
+      <c r="N11" s="54">
+        <f>IFERROR(M11/L11,0)</f>
+        <v>8.5526315789473686E-2</v>
+      </c>
+      <c r="O11">
+        <f>ABS(J11)</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B12" s="13" t="s">
         <v>74</v>
       </c>
@@ -1346,8 +2090,44 @@
       <c r="E12" s="23">
         <v>200000</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G12" s="57" t="str">
+        <f>TRIM($B$7)</f>
+        <v>Cost of revenue</v>
+      </c>
+      <c r="H12" s="53">
+        <f>$C$7</f>
+        <v>306000</v>
+      </c>
+      <c r="I12" s="53">
+        <f>$D$7</f>
+        <v>300000</v>
+      </c>
+      <c r="J12" s="53">
+        <f>H12-I12</f>
+        <v>6000</v>
+      </c>
+      <c r="K12" s="54">
+        <f>IFERROR(J12/I12,0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L12" s="53">
+        <f>$E$7</f>
+        <v>295000</v>
+      </c>
+      <c r="M12" s="53">
+        <f>H12-L12</f>
+        <v>11000</v>
+      </c>
+      <c r="N12" s="54">
+        <f>IFERROR(M12/L12,0)</f>
+        <v>3.7288135593220341E-2</v>
+      </c>
+      <c r="O12">
+        <f>ABS(J12)</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B13" s="13" t="s">
         <v>75</v>
       </c>
@@ -1360,8 +2140,44 @@
       <c r="E13" s="23">
         <v>152000</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G13" s="57" t="str">
+        <f>TRIM($B$12)</f>
+        <v>Research &amp; development</v>
+      </c>
+      <c r="H13" s="53">
+        <f>$C$12</f>
+        <v>210000</v>
+      </c>
+      <c r="I13" s="53">
+        <f>$D$12</f>
+        <v>205000</v>
+      </c>
+      <c r="J13" s="53">
+        <f>H13-I13</f>
+        <v>5000</v>
+      </c>
+      <c r="K13" s="54">
+        <f>IFERROR(J13/I13,0)</f>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="L13" s="53">
+        <f>$E$12</f>
+        <v>200000</v>
+      </c>
+      <c r="M13" s="53">
+        <f>H13-L13</f>
+        <v>10000</v>
+      </c>
+      <c r="N13" s="54">
+        <f>IFERROR(M13/L13,0)</f>
+        <v>0.05</v>
+      </c>
+      <c r="O13">
+        <f>ABS(J13)</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B14" s="13" t="s">
         <v>76</v>
       </c>
@@ -1374,8 +2190,44 @@
       <c r="E14" s="23">
         <v>98000</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G14" s="58" t="str">
+        <f>TRIM($B$14)</f>
+        <v>Customer success</v>
+      </c>
+      <c r="H14" s="55">
+        <f>$C$14</f>
+        <v>95000</v>
+      </c>
+      <c r="I14" s="55">
+        <f>$D$14</f>
+        <v>100000</v>
+      </c>
+      <c r="J14" s="55">
+        <f>H14-I14</f>
+        <v>-5000</v>
+      </c>
+      <c r="K14" s="56">
+        <f>IFERROR(J14/I14,0)</f>
+        <v>-0.05</v>
+      </c>
+      <c r="L14" s="55">
+        <f>$E$14</f>
+        <v>98000</v>
+      </c>
+      <c r="M14" s="55">
+        <f>H14-L14</f>
+        <v>-3000</v>
+      </c>
+      <c r="N14" s="56">
+        <f>IFERROR(M14/L14,0)</f>
+        <v>-3.0612244897959183E-2</v>
+      </c>
+      <c r="O14">
+        <f>ABS(J14)</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B15" s="24" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +2244,19 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:15" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="G16" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
+      <c r="K16" s="59"/>
+      <c r="L16" s="59"/>
+      <c r="M16" s="59"/>
+      <c r="N16" s="59"/>
+    </row>
+    <row r="17" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="24" t="s">
         <v>78</v>
       </c>
@@ -1408,8 +2272,112 @@
         <f>E8-E15</f>
         <v>185000</v>
       </c>
+      <c r="G17" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+    </row>
+    <row r="18" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G18" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="61"/>
+    </row>
+    <row r="19" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G19" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="61"/>
+    </row>
+    <row r="20" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G20" s="61" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+    </row>
+    <row r="21" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G21" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="61"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="61"/>
+    </row>
+    <row r="22" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G22" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="61"/>
+    </row>
+    <row r="23" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G23" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="62"/>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="G21:N21"/>
+    <mergeCell ref="G22:N22"/>
+    <mergeCell ref="G23:N23"/>
+    <mergeCell ref="G2:N2"/>
+    <mergeCell ref="G3:N3"/>
+    <mergeCell ref="G16:N16"/>
+    <mergeCell ref="G17:N17"/>
+    <mergeCell ref="G18:N18"/>
+    <mergeCell ref="G19:N19"/>
+  </mergeCells>
+  <conditionalFormatting sqref="J6:J14">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:J14">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
